--- a/outputs/Block5_Model_Stability_Summary.xlsx
+++ b/outputs/Block5_Model_Stability_Summary.xlsx
@@ -420,13 +420,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>66.431</v>
+        <v>78.65300000000001</v>
       </c>
       <c r="C2">
-        <v>2.391</v>
+        <v>1.479</v>
       </c>
       <c r="D2">
-        <v>1.352</v>
+        <v>0.365</v>
       </c>
       <c r="E2">
         <v>5.247</v>
@@ -437,10 +437,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>45.955</v>
+        <v>26.045</v>
       </c>
       <c r="C3">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -454,13 +454,13 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>63.918</v>
+        <v>66.76300000000001</v>
       </c>
       <c r="C4">
-        <v>0.592</v>
+        <v>0.603</v>
       </c>
       <c r="D4">
-        <v>0.487</v>
+        <v>0.36</v>
       </c>
       <c r="E4">
         <v>1.038</v>
